--- a/function/functionList_protocolCore.xlsx
+++ b/function/functionList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\function\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACDB3BA-48A5-470B-8131-B0F2B1D3C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F3E635-E1F0-4339-98EB-2AC10B4EF300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>Codice</t>
   </si>
@@ -70,6 +70,15 @@
   </si>
   <si>
     <t>YAX3C</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>Patch</t>
+  </si>
+  <si>
+    <t>AFC</t>
   </si>
 </sst>
 </file>
@@ -108,7 +117,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -202,11 +211,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -222,18 +270,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -514,42 +572,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -571,8 +636,11 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H2" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -591,11 +659,14 @@
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H3" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -603,8 +674,9 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -612,20 +684,24 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -633,6 +709,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
+      <c r="H9" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/function/functionList_protocolCore.xlsx
+++ b/function/functionList_protocolCore.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F3E635-E1F0-4339-98EB-2AC10B4EF300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23850" yWindow="2190" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -285,10 +285,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
